--- a/artfynd/A 29997-2024 artfynd.xlsx
+++ b/artfynd/A 29997-2024 artfynd.xlsx
@@ -1753,7 +1753,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713728</v>
+        <v>119713727</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467189</v>
+        <v>467570</v>
       </c>
       <c r="R11" t="n">
-        <v>7075104</v>
+        <v>7075272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713725</v>
+        <v>119713728</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467621</v>
+        <v>467189</v>
       </c>
       <c r="R13" t="n">
-        <v>7075343</v>
+        <v>7075104</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,6 +2043,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713727</v>
+        <v>119713725</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,21 +2090,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2109,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467570</v>
+        <v>467621</v>
       </c>
       <c r="R14" t="n">
-        <v>7075272</v>
+        <v>7075343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,11 +2150,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 29997-2024 artfynd.xlsx
+++ b/artfynd/A 29997-2024 artfynd.xlsx
@@ -1651,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713724</v>
+        <v>119713727</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,21 +1667,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467592</v>
+        <v>467570</v>
       </c>
       <c r="R10" t="n">
-        <v>7074950</v>
+        <v>7075272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,6 +1727,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713727</v>
+        <v>119713725</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,21 +1774,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1793,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467570</v>
+        <v>467621</v>
       </c>
       <c r="R11" t="n">
-        <v>7075272</v>
+        <v>7075343</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,11 +1834,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1860,7 +1860,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713726</v>
+        <v>119713728</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467720</v>
+        <v>467189</v>
       </c>
       <c r="R12" t="n">
-        <v>7074920</v>
+        <v>7075104</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,7 +1967,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713728</v>
+        <v>119713726</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467189</v>
+        <v>467720</v>
       </c>
       <c r="R13" t="n">
-        <v>7075104</v>
+        <v>7074920</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713725</v>
+        <v>119713724</v>
       </c>
       <c r="B14" t="n">
         <v>90580</v>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467621</v>
+        <v>467592</v>
       </c>
       <c r="R14" t="n">
-        <v>7075343</v>
+        <v>7074950</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 29997-2024 artfynd.xlsx
+++ b/artfynd/A 29997-2024 artfynd.xlsx
@@ -1651,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713727</v>
+        <v>119713725</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,21 +1667,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467570</v>
+        <v>467621</v>
       </c>
       <c r="R10" t="n">
-        <v>7075272</v>
+        <v>7075343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,11 +1727,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713725</v>
+        <v>119713724</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467621</v>
+        <v>467592</v>
       </c>
       <c r="R11" t="n">
-        <v>7075343</v>
+        <v>7074950</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1860,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713728</v>
+        <v>119713726</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1900,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467189</v>
+        <v>467720</v>
       </c>
       <c r="R12" t="n">
-        <v>7075104</v>
+        <v>7074920</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1935,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119713726</v>
+        <v>119713728</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467720</v>
+        <v>467189</v>
       </c>
       <c r="R13" t="n">
-        <v>7074920</v>
+        <v>7075104</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2042,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119713724</v>
+        <v>119713727</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,21 +2085,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2114,10 +2109,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467592</v>
+        <v>467570</v>
       </c>
       <c r="R14" t="n">
-        <v>7074950</v>
+        <v>7075272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,6 +2145,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 29997-2024 artfynd.xlsx
+++ b/artfynd/A 29997-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>637991</v>
       </c>
       <c r="B2" t="n">
-        <v>103527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467715.2069152957</v>
+        <v>467715</v>
       </c>
       <c r="R2" t="n">
-        <v>7074818.391739291</v>
+        <v>7074818</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1932-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4870490</v>
+        <v>119713726</v>
       </c>
       <c r="B3" t="n">
-        <v>101322</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222395</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandbergets östra brant, Skärvången, Jmt</t>
+          <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467715.2069152957</v>
+        <v>467720</v>
       </c>
       <c r="R3" t="n">
-        <v>7074818.391739291</v>
+        <v>7074920</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,27 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Thorvald Lange</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,74 +868,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3766280</v>
+        <v>119713727</v>
       </c>
       <c r="B4" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandbergets östra brant, Skärvången, Jmt</t>
+          <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467715.2069152957</v>
+        <v>467570</v>
       </c>
       <c r="R4" t="n">
-        <v>7074818.391739291</v>
+        <v>7075272</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,27 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Thorvald Lange</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,74 +970,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2673256</v>
+        <v>119713728</v>
       </c>
       <c r="B5" t="n">
-        <v>95709</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandbergets östra brant, Skärvången, Jmt</t>
+          <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467715.2069152957</v>
+        <v>467189</v>
       </c>
       <c r="R5" t="n">
-        <v>7074818.391739291</v>
+        <v>7075104</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,27 +1051,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Thorvald Lange</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,58 +1072,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6459344</v>
+        <v>2565553</v>
       </c>
       <c r="B6" t="n">
-        <v>100516</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>225047</v>
+        <v>220107</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bergalm</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. montana</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Stokes) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467715.2069152957</v>
+        <v>467715</v>
       </c>
       <c r="R6" t="n">
-        <v>7074818.391739291</v>
+        <v>7074818</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1236,19 +1156,9 @@
           <t>1932-08-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,37 +1195,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2565553</v>
+        <v>2673256</v>
       </c>
       <c r="B7" t="n">
-        <v>105129</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220107</v>
+        <v>220250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467715.2069152957</v>
+        <v>467715</v>
       </c>
       <c r="R7" t="n">
-        <v>7074818.391739291</v>
+        <v>7074818</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1358,19 +1263,9 @@
           <t>1932-08-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1407,15 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4269101</v>
+        <v>3766280</v>
       </c>
       <c r="B8" t="n">
-        <v>96353</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>221423</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1447,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467715.2069152957</v>
+        <v>467715</v>
       </c>
       <c r="R8" t="n">
-        <v>7074818.391739291</v>
+        <v>7074818</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1480,19 +1370,9 @@
           <t>1932-08-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1529,15 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5318579</v>
+        <v>4269101</v>
       </c>
       <c r="B9" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1569,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467715.2069152957</v>
+        <v>467715</v>
       </c>
       <c r="R9" t="n">
-        <v>7074818.391739291</v>
+        <v>7074818</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1602,19 +1477,9 @@
           <t>1932-08-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1932-08-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1651,53 +1516,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713725</v>
+        <v>4870490</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>222395</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>sandberget, Jmt</t>
+          <t>Sandbergets östra brant, Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467621</v>
+        <v>467715</v>
       </c>
       <c r="R10" t="n">
-        <v>7075343</v>
+        <v>7074818</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,12 +1581,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>1932-08-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>1932-08-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Thorvald Lange</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,69 +1602,69 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713724</v>
+        <v>5318579</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>sandberget, Jmt</t>
+          <t>Sandbergets östra brant, Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467592</v>
+        <v>467715</v>
       </c>
       <c r="R11" t="n">
-        <v>7074950</v>
+        <v>7074818</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,12 +1688,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>1932-08-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>1932-08-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Thorvald Lange</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,69 +1709,69 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713726</v>
+        <v>6459344</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>225047</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bergalm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ulmus glabra subsp. montana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Stokes) Hyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>sandberget, Jmt</t>
+          <t>Sandbergets östra brant, Skärvången, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467720</v>
+        <v>467715</v>
       </c>
       <c r="R12" t="n">
-        <v>7074920</v>
+        <v>7074818</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,17 +1795,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>1932-08-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>1932-08-27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Thorvald Lange</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,233 +1816,24 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>119713728</v>
-      </c>
-      <c r="B13" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>sandberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>467189</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7075104</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>119713727</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>sandberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>467570</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7075272</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
